--- a/benchmarks/LIGHTGBM_V3_FORECASTING/lgbm_results.xlsx
+++ b/benchmarks/LIGHTGBM_V3_FORECASTING/lgbm_results.xlsx
@@ -473,13 +473,13 @@
         <v>2021</v>
       </c>
       <c r="D2" t="n">
-        <v>5.898269946042637</v>
+        <v>5.907423877025592</v>
       </c>
       <c r="E2" t="n">
-        <v>24.20359652039575</v>
+        <v>24.88842912268654</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7463230118546322</v>
+        <v>0.735916727748023</v>
       </c>
     </row>
     <row r="3">
@@ -493,13 +493,13 @@
         <v>2022</v>
       </c>
       <c r="D3" t="n">
-        <v>14.09555589079379</v>
+        <v>14.18504756785659</v>
       </c>
       <c r="E3" t="n">
-        <v>55.57360599412179</v>
+        <v>55.83928752472882</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7797997466401684</v>
+        <v>0.7837613895482265</v>
       </c>
     </row>
     <row r="4">
@@ -513,13 +513,13 @@
         <v>2023</v>
       </c>
       <c r="D4" t="n">
-        <v>16.05749299410774</v>
+        <v>14.38417080585441</v>
       </c>
       <c r="E4" t="n">
-        <v>62.90579387759727</v>
+        <v>54.87140157879461</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7359766101625309</v>
+        <v>0.7904071836396528</v>
       </c>
     </row>
     <row r="5">
@@ -533,13 +533,13 @@
         <v>2024</v>
       </c>
       <c r="D5" t="n">
-        <v>34.97112207121172</v>
+        <v>33.23487268422488</v>
       </c>
       <c r="E5" t="n">
-        <v>110.2210123816302</v>
+        <v>107.5514833165882</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8235806936588642</v>
+        <v>0.8368463674328056</v>
       </c>
     </row>
     <row r="6">
@@ -553,13 +553,13 @@
         <v>2025</v>
       </c>
       <c r="D6" t="n">
-        <v>17.00711935929432</v>
+        <v>14.73475028416157</v>
       </c>
       <c r="E6" t="n">
-        <v>46.62551576797416</v>
+        <v>43.40737756350631</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8360311685008722</v>
+        <v>0.8578846131292227</v>
       </c>
     </row>
   </sheetData>
@@ -600,10 +600,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17.60591205229004</v>
+        <v>16.4892530438246</v>
       </c>
       <c r="C2" t="n">
-        <v>10.65009574298181</v>
+        <v>10.06491306090173</v>
       </c>
     </row>
     <row r="3">
@@ -613,10 +613,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>59.90590490834383</v>
+        <v>57.3115958212609</v>
       </c>
       <c r="C3" t="n">
-        <v>31.66386642415203</v>
+        <v>30.72766489389882</v>
       </c>
     </row>
     <row r="4">
@@ -626,10 +626,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7843422461634135</v>
+        <v>0.8009632562995861</v>
       </c>
       <c r="C4" t="n">
-        <v>0.04476810158856316</v>
+        <v>0.04786967801821013</v>
       </c>
     </row>
   </sheetData>
@@ -643,7 +643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B69"/>
+  <dimension ref="A1:B67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>545.6</v>
+        <v>565.2</v>
       </c>
     </row>
     <row r="3">
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>520.8</v>
+        <v>463.6</v>
       </c>
     </row>
     <row r="4">
@@ -685,323 +685,323 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>166.8</v>
+        <v>232</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>casos_roll4_mean</t>
+          <t>casos_lag_2</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>128</v>
+        <v>122.2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>casos_lag_2</t>
+          <t>casos_roll4_mean</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>119.6</v>
+        <v>110.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>semana</t>
+          <t>Rt_lag_1</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>103.6</v>
+        <v>87.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Rt_lag_1</t>
+          <t>Rt_lag_2</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>78.40000000000001</v>
+        <v>70.59999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>anio</t>
+          <t>mes</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>54.6</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>casos_roll8_mean</t>
+          <t>nino34</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>54</v>
+        <v>57.2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Rt_lag_2</t>
+          <t>casos_lag_8</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>50.6</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>casos_lag_8</t>
+          <t>casos_roll8_mean</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>casos_lag_4</t>
+          <t>pct_cropland</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>41.8</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>nino34</t>
+          <t>casos_lag_4</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>39.8</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>pct_cropland</t>
+          <t>tempmed_lag_1</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Rt_lag_4</t>
+          <t>EVI_mean</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>31</v>
+        <v>33.6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>umidmed_lag_4</t>
+          <t>precip_roll8_sum</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>26.2</v>
+        <v>33.2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>tempmin</t>
+          <t>umidmed_lag_4</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>25</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>pct_tree_cover</t>
+          <t>Rt_lag_4</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>24.8</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>soi</t>
+          <t>precip_total_semana_lag_4</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>24</v>
+        <v>26.6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>precip_roll4_sum</t>
+          <t>pct_shrubland</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>23.6</v>
+        <v>26.6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>LST_Day_mean</t>
+          <t>pct_tree_cover</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>23.4</v>
+        <v>25.4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>LST_Night_mean</t>
+          <t>soi</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>22.4</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>pct_wetland</t>
+          <t>area_km2</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>22</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>EVI_mean</t>
+          <t>tempmin</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>21.8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>male_population_pct</t>
+          <t>LST_Night_mean</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>20.4</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>mes</t>
+          <t>tempmed_lag_4</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>NDVI_mean</t>
+          <t>pct_builtup</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>20</v>
+        <v>20.6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>precip_total_semana_lag_4</t>
+          <t>population_density</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>19.8</v>
+        <v>20.6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>precip_roll8_sum</t>
+          <t>pct_wetland</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>18.4</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>precip_total_semana_lag_1</t>
+          <t>precip_roll4_sum</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>18.4</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>aging_index</t>
+          <t>NDVI_mean</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>17.8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>tempmed_lag_1</t>
+          <t>garbage_collection_pct</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>17.8</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>population_density</t>
+          <t>LST_Day_mean</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>17.8</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>umidmax</t>
+          <t>pct_grassland</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>17.6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>garbage_collection_pct</t>
+          <t>aging_index</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1011,17 +1011,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>elev_max</t>
+          <t>pct_water</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>17.4</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>tempmed</t>
+          <t>precip_total_semana</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -1031,311 +1031,291 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>area_km2</t>
+          <t>male_population_pct</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>16.8</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>tempmax</t>
+          <t>umidmax</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>16.6</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>pct_water</t>
+          <t>elev_mean</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>15.8</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>tempmed_lag_4</t>
+          <t>tempmed_roll8_mean</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>15.8</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>umidmed</t>
+          <t>n_pixels</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>15.2</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>pct_builtup</t>
+          <t>precip_total_semana_lag_1</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>14</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>n_pixels</t>
+          <t>water_supply_pct</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>13.8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>pct_shrubland</t>
+          <t>precip_max_semana</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>13.6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>water_supply_pct</t>
+          <t>LST_Day_std</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>13.4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>tempmed_roll4_mean</t>
+          <t>tempmed</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>13.4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>umidmin</t>
+          <t>LST_Night_std</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>13</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>umidmed_lag_1</t>
+          <t>median_age</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>12.8</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>LST_Night_std</t>
+          <t>pct_bare_sparse</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>12</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>pct_grassland</t>
+          <t>elev_max</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>11.8</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>pct_bare_sparse</t>
+          <t>NDVI_std</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>11.8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>female_population_pct</t>
+          <t>sewage_pct</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>11.4</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>tempmed_roll8_mean</t>
+          <t>umidmed_lag_1</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>11.4</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>precip_total_semana</t>
+          <t>umidmed</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>11</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>EVI_std</t>
+          <t>tempmax</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>10.4</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>NDVI_std</t>
+          <t>EVI_std</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>10.4</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>LST_Day_std</t>
+          <t>tempmed_roll4_mean</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>10</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>median_age</t>
+          <t>elev_min</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>9.800000000000001</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>elev_mean</t>
+          <t>precip_media_semana</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>9.6</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>sewage_pct</t>
+          <t>female_population_pct</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>8.800000000000001</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>precip_max_semana</t>
+          <t>umidmin</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>8.199999999999999</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>sex_ratio</t>
+          <t>dias_lluvia_semana</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>elev_min</t>
+          <t>sex_ratio</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>5</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>precip_media_semana</t>
+          <t>n_tiles</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>4.8</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>dias_lluvia_semana</t>
+          <t>pct_mangroves</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>n_tiles</t>
-        </is>
-      </c>
-      <c r="B68" t="n">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>pct_mangroves</t>
-        </is>
-      </c>
-      <c r="B69" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
   </sheetData>
